--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.31346</v>
+        <v>16.855</v>
       </c>
       <c r="D2" t="n">
-        <v>16.54176</v>
+        <v>16.62138</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81457</v>
+        <v>16.72146</v>
       </c>
       <c r="F2" t="n">
-        <v>42.18424</v>
+        <v>42.84347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05071</v>
+        <v>0.04946</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80059</v>
+        <v>1.78487</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.4165</v>
+        <v>16.66288</v>
       </c>
       <c r="D3" t="n">
-        <v>16.67786</v>
+        <v>16.42495</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64835</v>
+        <v>16.49074</v>
       </c>
       <c r="F3" t="n">
-        <v>42.784</v>
+        <v>42.49307</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05072</v>
+        <v>0.0492</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78576</v>
+        <v>1.82437</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.05929</v>
+        <v>16.70734</v>
       </c>
       <c r="D4" t="n">
-        <v>16.13824</v>
+        <v>16.31239</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77637</v>
+        <v>16.41654</v>
       </c>
       <c r="F4" t="n">
-        <v>42.81411</v>
+        <v>42.84571</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04958</v>
+        <v>0.05044</v>
       </c>
       <c r="H4" t="n">
-        <v>1.75499</v>
+        <v>1.82357</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.59122</v>
+        <v>16.77517</v>
       </c>
       <c r="D5" t="n">
-        <v>16.2632</v>
+        <v>16.35864</v>
       </c>
       <c r="E5" t="n">
-        <v>16.30669</v>
+        <v>16.75435</v>
       </c>
       <c r="F5" t="n">
-        <v>42.49863</v>
+        <v>41.77805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04943</v>
+        <v>0.04935</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80653</v>
+        <v>1.83575</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.75027</v>
+        <v>16.82829</v>
       </c>
       <c r="D6" t="n">
-        <v>16.56817</v>
+        <v>16.43178</v>
       </c>
       <c r="E6" t="n">
-        <v>16.47809</v>
+        <v>16.482</v>
       </c>
       <c r="F6" t="n">
-        <v>43.05779</v>
+        <v>42.05333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05065</v>
+        <v>0.05014</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82574</v>
+        <v>1.81185</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.46499</v>
+        <v>16.92237</v>
       </c>
       <c r="D7" t="n">
-        <v>16.28555</v>
+        <v>16.41168</v>
       </c>
       <c r="E7" t="n">
-        <v>16.79421</v>
+        <v>16.76567</v>
       </c>
       <c r="F7" t="n">
-        <v>42.09037</v>
+        <v>42.09463</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05059</v>
+        <v>0.05007</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81811</v>
+        <v>1.78341</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.74359</v>
+        <v>16.94853</v>
       </c>
       <c r="D8" t="n">
-        <v>16.45136</v>
+        <v>16.46512</v>
       </c>
       <c r="E8" t="n">
-        <v>16.97995</v>
+        <v>16.60526</v>
       </c>
       <c r="F8" t="n">
-        <v>42.81714</v>
+        <v>43.3928</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0513</v>
+        <v>0.0501</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79945</v>
+        <v>1.79594</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.33062</v>
+        <v>16.88305</v>
       </c>
       <c r="D9" t="n">
-        <v>16.60381</v>
+        <v>16.54914</v>
       </c>
       <c r="E9" t="n">
-        <v>16.81235</v>
+        <v>16.63663</v>
       </c>
       <c r="F9" t="n">
-        <v>42.72418</v>
+        <v>42.22233</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04943</v>
+        <v>0.05064</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83881</v>
+        <v>1.83122</v>
       </c>
     </row>
     <row r="10">
@@ -660,386 +660,1210 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.86328</v>
+        <v>17.20253</v>
       </c>
       <c r="D10" t="n">
-        <v>16.35316</v>
+        <v>16.51218</v>
       </c>
       <c r="E10" t="n">
-        <v>16.39087</v>
+        <v>16.53221</v>
       </c>
       <c r="F10" t="n">
-        <v>42.75893</v>
+        <v>42.75974</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05027</v>
+        <v>0.04994</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81089</v>
+        <v>1.76289</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.27775</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.44686</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.41024</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.09694</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05007</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.79597</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.03624</v>
+        <v>16.80221</v>
       </c>
       <c r="D12" t="n">
-        <v>16.5224</v>
+        <v>16.20319</v>
       </c>
       <c r="E12" t="n">
-        <v>16.39968</v>
+        <v>16.76931</v>
       </c>
       <c r="F12" t="n">
-        <v>41.62149</v>
+        <v>41.3585</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05025</v>
+        <v>0.05057</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81473</v>
+        <v>1.80781</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.72033</v>
+        <v>16.80687</v>
       </c>
       <c r="D13" t="n">
-        <v>16.71434</v>
+        <v>16.61155</v>
       </c>
       <c r="E13" t="n">
-        <v>16.28526</v>
+        <v>16.62568</v>
       </c>
       <c r="F13" t="n">
-        <v>41.73769</v>
+        <v>41.96573</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04962</v>
+        <v>0.05032</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82087</v>
+        <v>1.8075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.58714</v>
+        <v>16.64254</v>
       </c>
       <c r="D14" t="n">
-        <v>16.2898</v>
+        <v>16.40731</v>
       </c>
       <c r="E14" t="n">
-        <v>16.42474</v>
+        <v>16.62105</v>
       </c>
       <c r="F14" t="n">
-        <v>42.20145</v>
+        <v>41.91311</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05126</v>
+        <v>0.05024</v>
       </c>
       <c r="H14" t="n">
-        <v>1.79408</v>
+        <v>1.79616</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.76632</v>
+        <v>17.13128</v>
       </c>
       <c r="D15" t="n">
-        <v>16.87932</v>
+        <v>16.14207</v>
       </c>
       <c r="E15" t="n">
-        <v>16.47047</v>
+        <v>16.62671</v>
       </c>
       <c r="F15" t="n">
-        <v>41.88487</v>
+        <v>42.24647</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05072</v>
+        <v>0.05024</v>
       </c>
       <c r="H15" t="n">
-        <v>1.80583</v>
+        <v>1.83747</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.12435</v>
+        <v>16.6942</v>
       </c>
       <c r="D16" t="n">
-        <v>16.43003</v>
+        <v>16.50524</v>
       </c>
       <c r="E16" t="n">
-        <v>16.87512</v>
+        <v>16.67586</v>
       </c>
       <c r="F16" t="n">
-        <v>42.95796</v>
+        <v>43.3449</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0496</v>
+        <v>0.04957</v>
       </c>
       <c r="H16" t="n">
-        <v>1.80928</v>
+        <v>1.80381</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.99729</v>
+        <v>16.81236</v>
       </c>
       <c r="D17" t="n">
-        <v>16.88494</v>
+        <v>16.65268</v>
       </c>
       <c r="E17" t="n">
-        <v>16.74541</v>
+        <v>16.74277</v>
       </c>
       <c r="F17" t="n">
-        <v>42.4985</v>
+        <v>42.16942</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05058</v>
+        <v>0.05059</v>
       </c>
       <c r="H17" t="n">
-        <v>1.75206</v>
+        <v>1.81419</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.73556</v>
+        <v>16.7006</v>
       </c>
       <c r="D18" t="n">
-        <v>16.65602</v>
+        <v>16.4049</v>
       </c>
       <c r="E18" t="n">
-        <v>16.69836</v>
+        <v>16.59095</v>
       </c>
       <c r="F18" t="n">
-        <v>42.55454</v>
+        <v>42.23993</v>
       </c>
       <c r="G18" t="n">
         <v>0.05019</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76241</v>
+        <v>1.7794</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16.90136</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.62177</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.7546</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.04258</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05013</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.81625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>16.84741</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.28157</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.74846</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.40118</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.04999</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.81736</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="C20" t="n">
+        <v>16.79917</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.51727</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.69874</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.56067</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.83027</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.60315</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.08813</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.60927</v>
+        <v>15.60386</v>
       </c>
       <c r="D22" t="n">
-        <v>1.10682</v>
+        <v>15.5023</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.50516</v>
+      </c>
+      <c r="F22" t="n">
+        <v>254.67294</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.60712</v>
+        <v>15.76673</v>
       </c>
       <c r="D23" t="n">
-        <v>1.09366</v>
+        <v>15.35724</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.68861</v>
+      </c>
+      <c r="F23" t="n">
+        <v>255.80878</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.59909</v>
+        <v>15.69926</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1152</v>
+        <v>15.63701</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.68539</v>
+      </c>
+      <c r="F24" t="n">
+        <v>250.97563</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.59681</v>
+        <v>15.86673</v>
       </c>
       <c r="D25" t="n">
-        <v>1.11107</v>
+        <v>15.31256</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.51791</v>
+      </c>
+      <c r="F25" t="n">
+        <v>253.60573</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.60322</v>
+        <v>15.62679</v>
       </c>
       <c r="D26" t="n">
-        <v>1.10462</v>
+        <v>15.18649</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.34185</v>
+      </c>
+      <c r="F26" t="n">
+        <v>253.79176</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.61613</v>
+        <v>15.87042</v>
       </c>
       <c r="D27" t="n">
-        <v>1.0919</v>
+        <v>15.27863</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.61142</v>
+      </c>
+      <c r="F27" t="n">
+        <v>250.86768</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.59767</v>
+        <v>15.44279</v>
       </c>
       <c r="D28" t="n">
-        <v>1.10504</v>
+        <v>15.11597</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.40181</v>
+      </c>
+      <c r="F28" t="n">
+        <v>255.04028</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.88124</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.50712</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.71905</v>
+      </c>
+      <c r="F29" t="n">
+        <v>251.69079</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.60545</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.10355</v>
+      <c r="C30" t="n">
+        <v>15.58025</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.34955</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.4887</v>
+      </c>
+      <c r="F30" t="n">
+        <v>252.31692</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.59689</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.79029</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.23051</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.63188</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.25367</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.45337</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.94204</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.44206</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.44243</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.1438</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.7739</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.6358</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15.98562</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.45302</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.50112</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.75454</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.9887</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.60978</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.38826</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.00227</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.67327</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.64525</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.40394</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.85389</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33.83671</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.37512</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.12933</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.1976</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.68745</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.79379</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.47269</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.88337</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.3371</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.97953</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.70146</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.28201</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.12426</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.23572</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.78004</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.59072</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.55863</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.78438</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.37948</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.32377</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.09891</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.73218</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.96876</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.68555</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.56029</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.99763</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.34515</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.60066</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.21371</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.40834</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.6814</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.61722</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.65704</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.23599</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.05966</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.81277</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.31129</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.23117</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.30814</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.8239</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.62748</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.49176</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.93225</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.04907</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.70063</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.58451</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.81077</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.51313</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.02853</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.45187</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.58238</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.64705</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.76399</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.36703</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.66237</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.06177</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.62807</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.9639</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.39763</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.41787</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.80113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.94042</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.02203</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.15693</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.66037</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.15818</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60941</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.10682</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.6034</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.10503</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60943</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.08916</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.59696</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.09655</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60153</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.10437</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60318</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.10666</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.5934199999999999</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.13428</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60371</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.11586</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.59997</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.11694</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.59979</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.12008</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.61226</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.10762</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61807</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.12831</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.60097</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.10892</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60667</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.11376</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60759</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.08914</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.09869</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.61308</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.13312</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.1217</v>
       </c>
     </row>
   </sheetData>
